--- a/docs/templates/3-statement-model-template.xlsx
+++ b/docs/templates/3-statement-model-template.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Balance Sheet" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Cash Flow" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Dashboard" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Monthly (optional)" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +27,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,6 +98,21 @@
       <color rgb="0055604F"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000000FF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="009C5700"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -128,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -158,6 +174,12 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -524,7 +546,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
@@ -543,6 +565,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -557,6 +580,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -567,10 +591,11 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Enter the client's name, reporting period, GST basis, and every trial balance line with its Category (pick from the dropdown) and Prior/Current period closing balances. Blue cells are the only ones to edit.</t>
-        </is>
-      </c>
-    </row>
+          <t>Enter the client's name, reporting period, entity type and GST basis (dropdowns in row 6), and every trial balance line (up to 200 accounts, rows 8–207) with its Category from the dropdown and Prior/Current period closing balances. Column E flags any row whose category is missing or misspelled — those rows are left out of every statement until fixed. Blue cells are the only ones to edit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -585,6 +610,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
@@ -599,6 +625,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -613,6 +640,20 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>6. Optional: Monthly tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Enter 12 months of revenue, net profit and month-end cash to draw the month-by-month charts on the client web dashboard. The tab checks its totals against the P&amp;L and its last cash figure against the Balance Sheet.</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
@@ -627,6 +668,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
@@ -649,13 +691,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:G207"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -672,6 +716,21 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Rows needing a category</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>COUNTIF($E$8:$E$207,"CHECK CATEGORY")</f>
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="str">
+        <f>IF(B3=0,"All rows categorised","Fix the rows marked CHECK CATEGORY in column E")</f>
+        <v>All rows categorised</v>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -709,6 +768,28 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Entity type</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>GST basis</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>Accruals</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
@@ -730,6 +811,16 @@
           <t>Current Period ($)</t>
         </is>
       </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Category check</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>Valid categories (exact spelling)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -748,6 +839,15 @@
       <c r="D8" s="8" t="n">
         <v>450000</v>
       </c>
+      <c r="E8" s="22" t="str">
+        <f>IF(AND(A8&amp;""="",B8&amp;""="",N(C8)=0,N(D8)=0),"",IF(COUNTIF($G$8:$G$20,B8&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v>OK</v>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -766,6 +866,15 @@
       <c r="D9" s="8" t="n">
         <v>220000</v>
       </c>
+      <c r="E9" s="22" t="str">
+        <f>IF(AND(A9&amp;""="",B9&amp;""="",N(C9)=0,N(D9)=0),"",IF(COUNTIF($G$8:$G$20,B9&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v>OK</v>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -784,6 +893,15 @@
       <c r="D10" s="8" t="n">
         <v>24000</v>
       </c>
+      <c r="E10" s="22" t="str">
+        <f>IF(AND(A10&amp;""="",B10&amp;""="",N(C10)=0,N(D10)=0),"",IF(COUNTIF($G$8:$G$20,B10&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v>OK</v>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -802,6 +920,15 @@
       <c r="D11" s="8" t="n">
         <v>105000</v>
       </c>
+      <c r="E11" s="22" t="str">
+        <f>IF(AND(A11&amp;""="",B11&amp;""="",N(C11)=0,N(D11)=0),"",IF(COUNTIF($G$8:$G$20,B11&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v>OK</v>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; Amortisation</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -820,6 +947,15 @@
       <c r="D12" s="8" t="n">
         <v>20000</v>
       </c>
+      <c r="E12" s="22" t="str">
+        <f>IF(AND(A12&amp;""="",B12&amp;""="",N(C12)=0,N(D12)=0),"",IF(COUNTIF($G$8:$G$20,B12&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v>OK</v>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Interest Expense</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -838,6 +974,15 @@
       <c r="D13" s="8" t="n">
         <v>6500</v>
       </c>
+      <c r="E13" s="22" t="str">
+        <f>IF(AND(A13&amp;""="",B13&amp;""="",N(C13)=0,N(D13)=0),"",IF(COUNTIF($G$8:$G$20,B13&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v>OK</v>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Tax Expense</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -856,6 +1001,15 @@
       <c r="D14" s="8" t="n">
         <v>4200</v>
       </c>
+      <c r="E14" s="22" t="str">
+        <f>IF(AND(A14&amp;""="",B14&amp;""="",N(C14)=0,N(D14)=0),"",IF(COUNTIF($G$8:$G$20,B14&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v>OK</v>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -874,6 +1028,15 @@
       <c r="D15" s="8" t="n">
         <v>3300</v>
       </c>
+      <c r="E15" s="22" t="str">
+        <f>IF(AND(A15&amp;""="",B15&amp;""="",N(C15)=0,N(D15)=0),"",IF(COUNTIF($G$8:$G$20,B15&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v>OK</v>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -892,6 +1055,15 @@
       <c r="D16" s="8" t="n">
         <v>14000</v>
       </c>
+      <c r="E16" s="22" t="str">
+        <f>IF(AND(A16&amp;""="",B16&amp;""="",N(C16)=0,N(D16)=0),"",IF(COUNTIF($G$8:$G$20,B16&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v>OK</v>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Non-Current Assets</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -910,6 +1082,15 @@
       <c r="D17" s="8" t="n">
         <v>4500</v>
       </c>
+      <c r="E17" s="22" t="str">
+        <f>IF(AND(A17&amp;""="",B17&amp;""="",N(C17)=0,N(D17)=0),"",IF(COUNTIF($G$8:$G$20,B17&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v>OK</v>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -928,6 +1109,15 @@
       <c r="D18" s="8" t="n">
         <v>12000</v>
       </c>
+      <c r="E18" s="22" t="str">
+        <f>IF(AND(A18&amp;""="",B18&amp;""="",N(C18)=0,N(D18)=0),"",IF(COUNTIF($G$8:$G$20,B18&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v>OK</v>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Non-Current Liabilities</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -946,6 +1136,15 @@
       <c r="D19" s="8" t="n">
         <v>39000</v>
       </c>
+      <c r="E19" s="22" t="str">
+        <f>IF(AND(A19&amp;""="",B19&amp;""="",N(C19)=0,N(D19)=0),"",IF(COUNTIF($G$8:$G$20,B19&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v>OK</v>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Share Capital</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -964,6 +1163,15 @@
       <c r="D20" s="8" t="n">
         <v>34000</v>
       </c>
+      <c r="E20" s="22" t="str">
+        <f>IF(AND(A20&amp;""="",B20&amp;""="",N(C20)=0,N(D20)=0),"",IF(COUNTIF($G$8:$G$20,B20&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v>OK</v>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Drawings/Dividends Paid</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -982,6 +1190,10 @@
       <c r="D21" s="8" t="n">
         <v>52000</v>
       </c>
+      <c r="E21" s="22" t="str">
+        <f>IF(AND(A21&amp;""="",B21&amp;""="",N(C21)=0,N(D21)=0),"",IF(COUNTIF($G$8:$G$20,B21&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1000,6 +1212,10 @@
       <c r="D22" s="8" t="n">
         <v>70000</v>
       </c>
+      <c r="E22" s="22" t="str">
+        <f>IF(AND(A22&amp;""="",B22&amp;""="",N(C22)=0,N(D22)=0),"",IF(COUNTIF($G$8:$G$20,B22&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1018,6 +1234,10 @@
       <c r="D23" s="8" t="n">
         <v>26000</v>
       </c>
+      <c r="E23" s="22" t="str">
+        <f>IF(AND(A23&amp;""="",B23&amp;""="",N(C23)=0,N(D23)=0),"",IF(COUNTIF($G$8:$G$20,B23&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1036,6 +1256,10 @@
       <c r="D24" s="8" t="n">
         <v>7500</v>
       </c>
+      <c r="E24" s="22" t="str">
+        <f>IF(AND(A24&amp;""="",B24&amp;""="",N(C24)=0,N(D24)=0),"",IF(COUNTIF($G$8:$G$20,B24&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1054,11 +1278,15 @@
       <c r="D25" s="8" t="n">
         <v>60000</v>
       </c>
+      <c r="E25" s="22" t="str">
+        <f>IF(AND(A25&amp;""="",B25&amp;""="",N(C25)=0,N(D25)=0),"",IF(COUNTIF($G$8:$G$20,B25&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Owner's Capital</t>
+          <t>Share Capital (paid-up)</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -1072,11 +1300,15 @@
       <c r="D26" s="8" t="n">
         <v>50000</v>
       </c>
+      <c r="E26" s="22" t="str">
+        <f>IF(AND(A26&amp;""="",B26&amp;""="",N(C26)=0,N(D26)=0),"",IF(COUNTIF($G$8:$G$20,B26&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v>OK</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Owner Drawings</t>
+          <t>Dividends Paid</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -1090,103 +1322,1629 @@
       <c r="D27" s="8" t="n">
         <v>18000</v>
       </c>
+      <c r="E27" s="22" t="str">
+        <f>IF(AND(A27&amp;""="",B27&amp;""="",N(C27)=0,N(D27)=0),"",IF(COUNTIF($G$8:$G$20,B27&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="22" t="str">
+        <f>IF(AND(A28&amp;""="",B28&amp;""="",N(C28)=0,N(D28)=0),"",IF(COUNTIF($G$8:$G$20,B28&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Category reference (exact spelling the formulas key on):</t>
-        </is>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="22" t="str">
+        <f>IF(AND(A29&amp;""="",B29&amp;""="",N(C29)=0,N(D29)=0),"",IF(COUNTIF($G$8:$G$20,B29&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>• Revenue</t>
-        </is>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="22" t="str">
+        <f>IF(AND(A30&amp;""="",B30&amp;""="",N(C30)=0,N(D30)=0),"",IF(COUNTIF($G$8:$G$20,B30&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>• COGS</t>
-        </is>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="22" t="str">
+        <f>IF(AND(A31&amp;""="",B31&amp;""="",N(C31)=0,N(D31)=0),"",IF(COUNTIF($G$8:$G$20,B31&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>• Operating Expenses</t>
-        </is>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="22" t="str">
+        <f>IF(AND(A32&amp;""="",B32&amp;""="",N(C32)=0,N(D32)=0),"",IF(COUNTIF($G$8:$G$20,B32&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>• Depreciation &amp; Amortisation</t>
-        </is>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="22" t="str">
+        <f>IF(AND(A33&amp;""="",B33&amp;""="",N(C33)=0,N(D33)=0),"",IF(COUNTIF($G$8:$G$20,B33&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>• Interest Expense</t>
-        </is>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="22" t="str">
+        <f>IF(AND(A34&amp;""="",B34&amp;""="",N(C34)=0,N(D34)=0),"",IF(COUNTIF($G$8:$G$20,B34&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>• Tax Expense</t>
-        </is>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="22" t="str">
+        <f>IF(AND(A35&amp;""="",B35&amp;""="",N(C35)=0,N(D35)=0),"",IF(COUNTIF($G$8:$G$20,B35&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>• Cash</t>
-        </is>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="22" t="str">
+        <f>IF(AND(A36&amp;""="",B36&amp;""="",N(C36)=0,N(D36)=0),"",IF(COUNTIF($G$8:$G$20,B36&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>• Other Current Assets</t>
-        </is>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="22" t="str">
+        <f>IF(AND(A37&amp;""="",B37&amp;""="",N(C37)=0,N(D37)=0),"",IF(COUNTIF($G$8:$G$20,B37&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>• Non-Current Assets</t>
-        </is>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="22" t="str">
+        <f>IF(AND(A38&amp;""="",B38&amp;""="",N(C38)=0,N(D38)=0),"",IF(COUNTIF($G$8:$G$20,B38&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>• Current Liabilities</t>
-        </is>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="22" t="str">
+        <f>IF(AND(A39&amp;""="",B39&amp;""="",N(C39)=0,N(D39)=0),"",IF(COUNTIF($G$8:$G$20,B39&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>• Non-Current Liabilities</t>
-        </is>
+      <c r="B40" s="7" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="22" t="str">
+        <f>IF(AND(A40&amp;""="",B40&amp;""="",N(C40)=0,N(D40)=0),"",IF(COUNTIF($G$8:$G$20,B40&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>• Share Capital</t>
-        </is>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="8" t="n"/>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="22" t="str">
+        <f>IF(AND(A41&amp;""="",B41&amp;""="",N(C41)=0,N(D41)=0),"",IF(COUNTIF($G$8:$G$20,B41&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>• Drawings/Dividends Paid</t>
-        </is>
+      <c r="B42" s="7" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="22" t="str">
+        <f>IF(AND(A42&amp;""="",B42&amp;""="",N(C42)=0,N(D42)=0),"",IF(COUNTIF($G$8:$G$20,B42&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="22" t="str">
+        <f>IF(AND(A43&amp;""="",B43&amp;""="",N(C43)=0,N(D43)=0),"",IF(COUNTIF($G$8:$G$20,B43&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="7" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="22" t="str">
+        <f>IF(AND(A44&amp;""="",B44&amp;""="",N(C44)=0,N(D44)=0),"",IF(COUNTIF($G$8:$G$20,B44&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="7" t="n"/>
+      <c r="C45" s="8" t="n"/>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="22" t="str">
+        <f>IF(AND(A45&amp;""="",B45&amp;""="",N(C45)=0,N(D45)=0),"",IF(COUNTIF($G$8:$G$20,B45&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="7" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="22" t="str">
+        <f>IF(AND(A46&amp;""="",B46&amp;""="",N(C46)=0,N(D46)=0),"",IF(COUNTIF($G$8:$G$20,B46&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="22" t="str">
+        <f>IF(AND(A47&amp;""="",B47&amp;""="",N(C47)=0,N(D47)=0),"",IF(COUNTIF($G$8:$G$20,B47&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="7" t="n"/>
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="8" t="n"/>
+      <c r="E48" s="22" t="str">
+        <f>IF(AND(A48&amp;""="",B48&amp;""="",N(C48)=0,N(D48)=0),"",IF(COUNTIF($G$8:$G$20,B48&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="22" t="str">
+        <f>IF(AND(A49&amp;""="",B49&amp;""="",N(C49)=0,N(D49)=0),"",IF(COUNTIF($G$8:$G$20,B49&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="7" t="n"/>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="8" t="n"/>
+      <c r="E50" s="22" t="str">
+        <f>IF(AND(A50&amp;""="",B50&amp;""="",N(C50)=0,N(D50)=0),"",IF(COUNTIF($G$8:$G$20,B50&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="7" t="n"/>
+      <c r="C51" s="8" t="n"/>
+      <c r="D51" s="8" t="n"/>
+      <c r="E51" s="22" t="str">
+        <f>IF(AND(A51&amp;""="",B51&amp;""="",N(C51)=0,N(D51)=0),"",IF(COUNTIF($G$8:$G$20,B51&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="7" t="n"/>
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="8" t="n"/>
+      <c r="E52" s="22" t="str">
+        <f>IF(AND(A52&amp;""="",B52&amp;""="",N(C52)=0,N(D52)=0),"",IF(COUNTIF($G$8:$G$20,B52&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="7" t="n"/>
+      <c r="C53" s="8" t="n"/>
+      <c r="D53" s="8" t="n"/>
+      <c r="E53" s="22" t="str">
+        <f>IF(AND(A53&amp;""="",B53&amp;""="",N(C53)=0,N(D53)=0),"",IF(COUNTIF($G$8:$G$20,B53&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="7" t="n"/>
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="8" t="n"/>
+      <c r="E54" s="22" t="str">
+        <f>IF(AND(A54&amp;""="",B54&amp;""="",N(C54)=0,N(D54)=0),"",IF(COUNTIF($G$8:$G$20,B54&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="7" t="n"/>
+      <c r="C55" s="8" t="n"/>
+      <c r="D55" s="8" t="n"/>
+      <c r="E55" s="22" t="str">
+        <f>IF(AND(A55&amp;""="",B55&amp;""="",N(C55)=0,N(D55)=0),"",IF(COUNTIF($G$8:$G$20,B55&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="7" t="n"/>
+      <c r="C56" s="8" t="n"/>
+      <c r="D56" s="8" t="n"/>
+      <c r="E56" s="22" t="str">
+        <f>IF(AND(A56&amp;""="",B56&amp;""="",N(C56)=0,N(D56)=0),"",IF(COUNTIF($G$8:$G$20,B56&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="7" t="n"/>
+      <c r="C57" s="8" t="n"/>
+      <c r="D57" s="8" t="n"/>
+      <c r="E57" s="22" t="str">
+        <f>IF(AND(A57&amp;""="",B57&amp;""="",N(C57)=0,N(D57)=0),"",IF(COUNTIF($G$8:$G$20,B57&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="7" t="n"/>
+      <c r="C58" s="8" t="n"/>
+      <c r="D58" s="8" t="n"/>
+      <c r="E58" s="22" t="str">
+        <f>IF(AND(A58&amp;""="",B58&amp;""="",N(C58)=0,N(D58)=0),"",IF(COUNTIF($G$8:$G$20,B58&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="7" t="n"/>
+      <c r="C59" s="8" t="n"/>
+      <c r="D59" s="8" t="n"/>
+      <c r="E59" s="22" t="str">
+        <f>IF(AND(A59&amp;""="",B59&amp;""="",N(C59)=0,N(D59)=0),"",IF(COUNTIF($G$8:$G$20,B59&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="7" t="n"/>
+      <c r="C60" s="8" t="n"/>
+      <c r="D60" s="8" t="n"/>
+      <c r="E60" s="22" t="str">
+        <f>IF(AND(A60&amp;""="",B60&amp;""="",N(C60)=0,N(D60)=0),"",IF(COUNTIF($G$8:$G$20,B60&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="7" t="n"/>
+      <c r="C61" s="8" t="n"/>
+      <c r="D61" s="8" t="n"/>
+      <c r="E61" s="22" t="str">
+        <f>IF(AND(A61&amp;""="",B61&amp;""="",N(C61)=0,N(D61)=0),"",IF(COUNTIF($G$8:$G$20,B61&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="7" t="n"/>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="8" t="n"/>
+      <c r="E62" s="22" t="str">
+        <f>IF(AND(A62&amp;""="",B62&amp;""="",N(C62)=0,N(D62)=0),"",IF(COUNTIF($G$8:$G$20,B62&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="7" t="n"/>
+      <c r="C63" s="8" t="n"/>
+      <c r="D63" s="8" t="n"/>
+      <c r="E63" s="22" t="str">
+        <f>IF(AND(A63&amp;""="",B63&amp;""="",N(C63)=0,N(D63)=0),"",IF(COUNTIF($G$8:$G$20,B63&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="7" t="n"/>
+      <c r="C64" s="8" t="n"/>
+      <c r="D64" s="8" t="n"/>
+      <c r="E64" s="22" t="str">
+        <f>IF(AND(A64&amp;""="",B64&amp;""="",N(C64)=0,N(D64)=0),"",IF(COUNTIF($G$8:$G$20,B64&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="7" t="n"/>
+      <c r="C65" s="8" t="n"/>
+      <c r="D65" s="8" t="n"/>
+      <c r="E65" s="22" t="str">
+        <f>IF(AND(A65&amp;""="",B65&amp;""="",N(C65)=0,N(D65)=0),"",IF(COUNTIF($G$8:$G$20,B65&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="7" t="n"/>
+      <c r="C66" s="8" t="n"/>
+      <c r="D66" s="8" t="n"/>
+      <c r="E66" s="22" t="str">
+        <f>IF(AND(A66&amp;""="",B66&amp;""="",N(C66)=0,N(D66)=0),"",IF(COUNTIF($G$8:$G$20,B66&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="7" t="n"/>
+      <c r="C67" s="8" t="n"/>
+      <c r="D67" s="8" t="n"/>
+      <c r="E67" s="22" t="str">
+        <f>IF(AND(A67&amp;""="",B67&amp;""="",N(C67)=0,N(D67)=0),"",IF(COUNTIF($G$8:$G$20,B67&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="7" t="n"/>
+      <c r="C68" s="8" t="n"/>
+      <c r="D68" s="8" t="n"/>
+      <c r="E68" s="22" t="str">
+        <f>IF(AND(A68&amp;""="",B68&amp;""="",N(C68)=0,N(D68)=0),"",IF(COUNTIF($G$8:$G$20,B68&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="7" t="n"/>
+      <c r="C69" s="8" t="n"/>
+      <c r="D69" s="8" t="n"/>
+      <c r="E69" s="22" t="str">
+        <f>IF(AND(A69&amp;""="",B69&amp;""="",N(C69)=0,N(D69)=0),"",IF(COUNTIF($G$8:$G$20,B69&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="7" t="n"/>
+      <c r="C70" s="8" t="n"/>
+      <c r="D70" s="8" t="n"/>
+      <c r="E70" s="22" t="str">
+        <f>IF(AND(A70&amp;""="",B70&amp;""="",N(C70)=0,N(D70)=0),"",IF(COUNTIF($G$8:$G$20,B70&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="8" t="n"/>
+      <c r="D71" s="8" t="n"/>
+      <c r="E71" s="22" t="str">
+        <f>IF(AND(A71&amp;""="",B71&amp;""="",N(C71)=0,N(D71)=0),"",IF(COUNTIF($G$8:$G$20,B71&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="7" t="n"/>
+      <c r="C72" s="8" t="n"/>
+      <c r="D72" s="8" t="n"/>
+      <c r="E72" s="22" t="str">
+        <f>IF(AND(A72&amp;""="",B72&amp;""="",N(C72)=0,N(D72)=0),"",IF(COUNTIF($G$8:$G$20,B72&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="7" t="n"/>
+      <c r="C73" s="8" t="n"/>
+      <c r="D73" s="8" t="n"/>
+      <c r="E73" s="22" t="str">
+        <f>IF(AND(A73&amp;""="",B73&amp;""="",N(C73)=0,N(D73)=0),"",IF(COUNTIF($G$8:$G$20,B73&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="7" t="n"/>
+      <c r="C74" s="8" t="n"/>
+      <c r="D74" s="8" t="n"/>
+      <c r="E74" s="22" t="str">
+        <f>IF(AND(A74&amp;""="",B74&amp;""="",N(C74)=0,N(D74)=0),"",IF(COUNTIF($G$8:$G$20,B74&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="7" t="n"/>
+      <c r="C75" s="8" t="n"/>
+      <c r="D75" s="8" t="n"/>
+      <c r="E75" s="22" t="str">
+        <f>IF(AND(A75&amp;""="",B75&amp;""="",N(C75)=0,N(D75)=0),"",IF(COUNTIF($G$8:$G$20,B75&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="7" t="n"/>
+      <c r="C76" s="8" t="n"/>
+      <c r="D76" s="8" t="n"/>
+      <c r="E76" s="22" t="str">
+        <f>IF(AND(A76&amp;""="",B76&amp;""="",N(C76)=0,N(D76)=0),"",IF(COUNTIF($G$8:$G$20,B76&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="7" t="n"/>
+      <c r="C77" s="8" t="n"/>
+      <c r="D77" s="8" t="n"/>
+      <c r="E77" s="22" t="str">
+        <f>IF(AND(A77&amp;""="",B77&amp;""="",N(C77)=0,N(D77)=0),"",IF(COUNTIF($G$8:$G$20,B77&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="7" t="n"/>
+      <c r="C78" s="8" t="n"/>
+      <c r="D78" s="8" t="n"/>
+      <c r="E78" s="22" t="str">
+        <f>IF(AND(A78&amp;""="",B78&amp;""="",N(C78)=0,N(D78)=0),"",IF(COUNTIF($G$8:$G$20,B78&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="7" t="n"/>
+      <c r="C79" s="8" t="n"/>
+      <c r="D79" s="8" t="n"/>
+      <c r="E79" s="22" t="str">
+        <f>IF(AND(A79&amp;""="",B79&amp;""="",N(C79)=0,N(D79)=0),"",IF(COUNTIF($G$8:$G$20,B79&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="7" t="n"/>
+      <c r="C80" s="8" t="n"/>
+      <c r="D80" s="8" t="n"/>
+      <c r="E80" s="22" t="str">
+        <f>IF(AND(A80&amp;""="",B80&amp;""="",N(C80)=0,N(D80)=0),"",IF(COUNTIF($G$8:$G$20,B80&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="7" t="n"/>
+      <c r="C81" s="8" t="n"/>
+      <c r="D81" s="8" t="n"/>
+      <c r="E81" s="22" t="str">
+        <f>IF(AND(A81&amp;""="",B81&amp;""="",N(C81)=0,N(D81)=0),"",IF(COUNTIF($G$8:$G$20,B81&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="7" t="n"/>
+      <c r="C82" s="8" t="n"/>
+      <c r="D82" s="8" t="n"/>
+      <c r="E82" s="22" t="str">
+        <f>IF(AND(A82&amp;""="",B82&amp;""="",N(C82)=0,N(D82)=0),"",IF(COUNTIF($G$8:$G$20,B82&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="7" t="n"/>
+      <c r="C83" s="8" t="n"/>
+      <c r="D83" s="8" t="n"/>
+      <c r="E83" s="22" t="str">
+        <f>IF(AND(A83&amp;""="",B83&amp;""="",N(C83)=0,N(D83)=0),"",IF(COUNTIF($G$8:$G$20,B83&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="7" t="n"/>
+      <c r="C84" s="8" t="n"/>
+      <c r="D84" s="8" t="n"/>
+      <c r="E84" s="22" t="str">
+        <f>IF(AND(A84&amp;""="",B84&amp;""="",N(C84)=0,N(D84)=0),"",IF(COUNTIF($G$8:$G$20,B84&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="7" t="n"/>
+      <c r="C85" s="8" t="n"/>
+      <c r="D85" s="8" t="n"/>
+      <c r="E85" s="22" t="str">
+        <f>IF(AND(A85&amp;""="",B85&amp;""="",N(C85)=0,N(D85)=0),"",IF(COUNTIF($G$8:$G$20,B85&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="7" t="n"/>
+      <c r="C86" s="8" t="n"/>
+      <c r="D86" s="8" t="n"/>
+      <c r="E86" s="22" t="str">
+        <f>IF(AND(A86&amp;""="",B86&amp;""="",N(C86)=0,N(D86)=0),"",IF(COUNTIF($G$8:$G$20,B86&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="7" t="n"/>
+      <c r="C87" s="8" t="n"/>
+      <c r="D87" s="8" t="n"/>
+      <c r="E87" s="22" t="str">
+        <f>IF(AND(A87&amp;""="",B87&amp;""="",N(C87)=0,N(D87)=0),"",IF(COUNTIF($G$8:$G$20,B87&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="7" t="n"/>
+      <c r="C88" s="8" t="n"/>
+      <c r="D88" s="8" t="n"/>
+      <c r="E88" s="22" t="str">
+        <f>IF(AND(A88&amp;""="",B88&amp;""="",N(C88)=0,N(D88)=0),"",IF(COUNTIF($G$8:$G$20,B88&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="7" t="n"/>
+      <c r="C89" s="8" t="n"/>
+      <c r="D89" s="8" t="n"/>
+      <c r="E89" s="22" t="str">
+        <f>IF(AND(A89&amp;""="",B89&amp;""="",N(C89)=0,N(D89)=0),"",IF(COUNTIF($G$8:$G$20,B89&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="7" t="n"/>
+      <c r="C90" s="8" t="n"/>
+      <c r="D90" s="8" t="n"/>
+      <c r="E90" s="22" t="str">
+        <f>IF(AND(A90&amp;""="",B90&amp;""="",N(C90)=0,N(D90)=0),"",IF(COUNTIF($G$8:$G$20,B90&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="7" t="n"/>
+      <c r="C91" s="8" t="n"/>
+      <c r="D91" s="8" t="n"/>
+      <c r="E91" s="22" t="str">
+        <f>IF(AND(A91&amp;""="",B91&amp;""="",N(C91)=0,N(D91)=0),"",IF(COUNTIF($G$8:$G$20,B91&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="7" t="n"/>
+      <c r="C92" s="8" t="n"/>
+      <c r="D92" s="8" t="n"/>
+      <c r="E92" s="22" t="str">
+        <f>IF(AND(A92&amp;""="",B92&amp;""="",N(C92)=0,N(D92)=0),"",IF(COUNTIF($G$8:$G$20,B92&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="7" t="n"/>
+      <c r="C93" s="8" t="n"/>
+      <c r="D93" s="8" t="n"/>
+      <c r="E93" s="22" t="str">
+        <f>IF(AND(A93&amp;""="",B93&amp;""="",N(C93)=0,N(D93)=0),"",IF(COUNTIF($G$8:$G$20,B93&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="7" t="n"/>
+      <c r="C94" s="8" t="n"/>
+      <c r="D94" s="8" t="n"/>
+      <c r="E94" s="22" t="str">
+        <f>IF(AND(A94&amp;""="",B94&amp;""="",N(C94)=0,N(D94)=0),"",IF(COUNTIF($G$8:$G$20,B94&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="7" t="n"/>
+      <c r="C95" s="8" t="n"/>
+      <c r="D95" s="8" t="n"/>
+      <c r="E95" s="22" t="str">
+        <f>IF(AND(A95&amp;""="",B95&amp;""="",N(C95)=0,N(D95)=0),"",IF(COUNTIF($G$8:$G$20,B95&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="7" t="n"/>
+      <c r="C96" s="8" t="n"/>
+      <c r="D96" s="8" t="n"/>
+      <c r="E96" s="22" t="str">
+        <f>IF(AND(A96&amp;""="",B96&amp;""="",N(C96)=0,N(D96)=0),"",IF(COUNTIF($G$8:$G$20,B96&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="7" t="n"/>
+      <c r="C97" s="8" t="n"/>
+      <c r="D97" s="8" t="n"/>
+      <c r="E97" s="22" t="str">
+        <f>IF(AND(A97&amp;""="",B97&amp;""="",N(C97)=0,N(D97)=0),"",IF(COUNTIF($G$8:$G$20,B97&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="7" t="n"/>
+      <c r="C98" s="8" t="n"/>
+      <c r="D98" s="8" t="n"/>
+      <c r="E98" s="22" t="str">
+        <f>IF(AND(A98&amp;""="",B98&amp;""="",N(C98)=0,N(D98)=0),"",IF(COUNTIF($G$8:$G$20,B98&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="7" t="n"/>
+      <c r="C99" s="8" t="n"/>
+      <c r="D99" s="8" t="n"/>
+      <c r="E99" s="22" t="str">
+        <f>IF(AND(A99&amp;""="",B99&amp;""="",N(C99)=0,N(D99)=0),"",IF(COUNTIF($G$8:$G$20,B99&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="7" t="n"/>
+      <c r="C100" s="8" t="n"/>
+      <c r="D100" s="8" t="n"/>
+      <c r="E100" s="22" t="str">
+        <f>IF(AND(A100&amp;""="",B100&amp;""="",N(C100)=0,N(D100)=0),"",IF(COUNTIF($G$8:$G$20,B100&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="7" t="n"/>
+      <c r="C101" s="8" t="n"/>
+      <c r="D101" s="8" t="n"/>
+      <c r="E101" s="22" t="str">
+        <f>IF(AND(A101&amp;""="",B101&amp;""="",N(C101)=0,N(D101)=0),"",IF(COUNTIF($G$8:$G$20,B101&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="7" t="n"/>
+      <c r="C102" s="8" t="n"/>
+      <c r="D102" s="8" t="n"/>
+      <c r="E102" s="22" t="str">
+        <f>IF(AND(A102&amp;""="",B102&amp;""="",N(C102)=0,N(D102)=0),"",IF(COUNTIF($G$8:$G$20,B102&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="7" t="n"/>
+      <c r="C103" s="8" t="n"/>
+      <c r="D103" s="8" t="n"/>
+      <c r="E103" s="22" t="str">
+        <f>IF(AND(A103&amp;""="",B103&amp;""="",N(C103)=0,N(D103)=0),"",IF(COUNTIF($G$8:$G$20,B103&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="7" t="n"/>
+      <c r="C104" s="8" t="n"/>
+      <c r="D104" s="8" t="n"/>
+      <c r="E104" s="22" t="str">
+        <f>IF(AND(A104&amp;""="",B104&amp;""="",N(C104)=0,N(D104)=0),"",IF(COUNTIF($G$8:$G$20,B104&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="7" t="n"/>
+      <c r="C105" s="8" t="n"/>
+      <c r="D105" s="8" t="n"/>
+      <c r="E105" s="22" t="str">
+        <f>IF(AND(A105&amp;""="",B105&amp;""="",N(C105)=0,N(D105)=0),"",IF(COUNTIF($G$8:$G$20,B105&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="7" t="n"/>
+      <c r="C106" s="8" t="n"/>
+      <c r="D106" s="8" t="n"/>
+      <c r="E106" s="22" t="str">
+        <f>IF(AND(A106&amp;""="",B106&amp;""="",N(C106)=0,N(D106)=0),"",IF(COUNTIF($G$8:$G$20,B106&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="7" t="n"/>
+      <c r="C107" s="8" t="n"/>
+      <c r="D107" s="8" t="n"/>
+      <c r="E107" s="22" t="str">
+        <f>IF(AND(A107&amp;""="",B107&amp;""="",N(C107)=0,N(D107)=0),"",IF(COUNTIF($G$8:$G$20,B107&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="7" t="n"/>
+      <c r="C108" s="8" t="n"/>
+      <c r="D108" s="8" t="n"/>
+      <c r="E108" s="22" t="str">
+        <f>IF(AND(A108&amp;""="",B108&amp;""="",N(C108)=0,N(D108)=0),"",IF(COUNTIF($G$8:$G$20,B108&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="7" t="n"/>
+      <c r="C109" s="8" t="n"/>
+      <c r="D109" s="8" t="n"/>
+      <c r="E109" s="22" t="str">
+        <f>IF(AND(A109&amp;""="",B109&amp;""="",N(C109)=0,N(D109)=0),"",IF(COUNTIF($G$8:$G$20,B109&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="7" t="n"/>
+      <c r="C110" s="8" t="n"/>
+      <c r="D110" s="8" t="n"/>
+      <c r="E110" s="22" t="str">
+        <f>IF(AND(A110&amp;""="",B110&amp;""="",N(C110)=0,N(D110)=0),"",IF(COUNTIF($G$8:$G$20,B110&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="7" t="n"/>
+      <c r="C111" s="8" t="n"/>
+      <c r="D111" s="8" t="n"/>
+      <c r="E111" s="22" t="str">
+        <f>IF(AND(A111&amp;""="",B111&amp;""="",N(C111)=0,N(D111)=0),"",IF(COUNTIF($G$8:$G$20,B111&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="7" t="n"/>
+      <c r="C112" s="8" t="n"/>
+      <c r="D112" s="8" t="n"/>
+      <c r="E112" s="22" t="str">
+        <f>IF(AND(A112&amp;""="",B112&amp;""="",N(C112)=0,N(D112)=0),"",IF(COUNTIF($G$8:$G$20,B112&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="7" t="n"/>
+      <c r="C113" s="8" t="n"/>
+      <c r="D113" s="8" t="n"/>
+      <c r="E113" s="22" t="str">
+        <f>IF(AND(A113&amp;""="",B113&amp;""="",N(C113)=0,N(D113)=0),"",IF(COUNTIF($G$8:$G$20,B113&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="7" t="n"/>
+      <c r="C114" s="8" t="n"/>
+      <c r="D114" s="8" t="n"/>
+      <c r="E114" s="22" t="str">
+        <f>IF(AND(A114&amp;""="",B114&amp;""="",N(C114)=0,N(D114)=0),"",IF(COUNTIF($G$8:$G$20,B114&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="7" t="n"/>
+      <c r="C115" s="8" t="n"/>
+      <c r="D115" s="8" t="n"/>
+      <c r="E115" s="22" t="str">
+        <f>IF(AND(A115&amp;""="",B115&amp;""="",N(C115)=0,N(D115)=0),"",IF(COUNTIF($G$8:$G$20,B115&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="7" t="n"/>
+      <c r="C116" s="8" t="n"/>
+      <c r="D116" s="8" t="n"/>
+      <c r="E116" s="22" t="str">
+        <f>IF(AND(A116&amp;""="",B116&amp;""="",N(C116)=0,N(D116)=0),"",IF(COUNTIF($G$8:$G$20,B116&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="7" t="n"/>
+      <c r="C117" s="8" t="n"/>
+      <c r="D117" s="8" t="n"/>
+      <c r="E117" s="22" t="str">
+        <f>IF(AND(A117&amp;""="",B117&amp;""="",N(C117)=0,N(D117)=0),"",IF(COUNTIF($G$8:$G$20,B117&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="7" t="n"/>
+      <c r="C118" s="8" t="n"/>
+      <c r="D118" s="8" t="n"/>
+      <c r="E118" s="22" t="str">
+        <f>IF(AND(A118&amp;""="",B118&amp;""="",N(C118)=0,N(D118)=0),"",IF(COUNTIF($G$8:$G$20,B118&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="7" t="n"/>
+      <c r="C119" s="8" t="n"/>
+      <c r="D119" s="8" t="n"/>
+      <c r="E119" s="22" t="str">
+        <f>IF(AND(A119&amp;""="",B119&amp;""="",N(C119)=0,N(D119)=0),"",IF(COUNTIF($G$8:$G$20,B119&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="7" t="n"/>
+      <c r="C120" s="8" t="n"/>
+      <c r="D120" s="8" t="n"/>
+      <c r="E120" s="22" t="str">
+        <f>IF(AND(A120&amp;""="",B120&amp;""="",N(C120)=0,N(D120)=0),"",IF(COUNTIF($G$8:$G$20,B120&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="7" t="n"/>
+      <c r="C121" s="8" t="n"/>
+      <c r="D121" s="8" t="n"/>
+      <c r="E121" s="22" t="str">
+        <f>IF(AND(A121&amp;""="",B121&amp;""="",N(C121)=0,N(D121)=0),"",IF(COUNTIF($G$8:$G$20,B121&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="7" t="n"/>
+      <c r="C122" s="8" t="n"/>
+      <c r="D122" s="8" t="n"/>
+      <c r="E122" s="22" t="str">
+        <f>IF(AND(A122&amp;""="",B122&amp;""="",N(C122)=0,N(D122)=0),"",IF(COUNTIF($G$8:$G$20,B122&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="7" t="n"/>
+      <c r="C123" s="8" t="n"/>
+      <c r="D123" s="8" t="n"/>
+      <c r="E123" s="22" t="str">
+        <f>IF(AND(A123&amp;""="",B123&amp;""="",N(C123)=0,N(D123)=0),"",IF(COUNTIF($G$8:$G$20,B123&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="7" t="n"/>
+      <c r="C124" s="8" t="n"/>
+      <c r="D124" s="8" t="n"/>
+      <c r="E124" s="22" t="str">
+        <f>IF(AND(A124&amp;""="",B124&amp;""="",N(C124)=0,N(D124)=0),"",IF(COUNTIF($G$8:$G$20,B124&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="7" t="n"/>
+      <c r="C125" s="8" t="n"/>
+      <c r="D125" s="8" t="n"/>
+      <c r="E125" s="22" t="str">
+        <f>IF(AND(A125&amp;""="",B125&amp;""="",N(C125)=0,N(D125)=0),"",IF(COUNTIF($G$8:$G$20,B125&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="7" t="n"/>
+      <c r="C126" s="8" t="n"/>
+      <c r="D126" s="8" t="n"/>
+      <c r="E126" s="22" t="str">
+        <f>IF(AND(A126&amp;""="",B126&amp;""="",N(C126)=0,N(D126)=0),"",IF(COUNTIF($G$8:$G$20,B126&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="7" t="n"/>
+      <c r="C127" s="8" t="n"/>
+      <c r="D127" s="8" t="n"/>
+      <c r="E127" s="22" t="str">
+        <f>IF(AND(A127&amp;""="",B127&amp;""="",N(C127)=0,N(D127)=0),"",IF(COUNTIF($G$8:$G$20,B127&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="7" t="n"/>
+      <c r="C128" s="8" t="n"/>
+      <c r="D128" s="8" t="n"/>
+      <c r="E128" s="22" t="str">
+        <f>IF(AND(A128&amp;""="",B128&amp;""="",N(C128)=0,N(D128)=0),"",IF(COUNTIF($G$8:$G$20,B128&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" s="7" t="n"/>
+      <c r="C129" s="8" t="n"/>
+      <c r="D129" s="8" t="n"/>
+      <c r="E129" s="22" t="str">
+        <f>IF(AND(A129&amp;""="",B129&amp;""="",N(C129)=0,N(D129)=0),"",IF(COUNTIF($G$8:$G$20,B129&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="7" t="n"/>
+      <c r="C130" s="8" t="n"/>
+      <c r="D130" s="8" t="n"/>
+      <c r="E130" s="22" t="str">
+        <f>IF(AND(A130&amp;""="",B130&amp;""="",N(C130)=0,N(D130)=0),"",IF(COUNTIF($G$8:$G$20,B130&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" s="7" t="n"/>
+      <c r="C131" s="8" t="n"/>
+      <c r="D131" s="8" t="n"/>
+      <c r="E131" s="22" t="str">
+        <f>IF(AND(A131&amp;""="",B131&amp;""="",N(C131)=0,N(D131)=0),"",IF(COUNTIF($G$8:$G$20,B131&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="7" t="n"/>
+      <c r="C132" s="8" t="n"/>
+      <c r="D132" s="8" t="n"/>
+      <c r="E132" s="22" t="str">
+        <f>IF(AND(A132&amp;""="",B132&amp;""="",N(C132)=0,N(D132)=0),"",IF(COUNTIF($G$8:$G$20,B132&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" s="7" t="n"/>
+      <c r="C133" s="8" t="n"/>
+      <c r="D133" s="8" t="n"/>
+      <c r="E133" s="22" t="str">
+        <f>IF(AND(A133&amp;""="",B133&amp;""="",N(C133)=0,N(D133)=0),"",IF(COUNTIF($G$8:$G$20,B133&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="7" t="n"/>
+      <c r="C134" s="8" t="n"/>
+      <c r="D134" s="8" t="n"/>
+      <c r="E134" s="22" t="str">
+        <f>IF(AND(A134&amp;""="",B134&amp;""="",N(C134)=0,N(D134)=0),"",IF(COUNTIF($G$8:$G$20,B134&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" s="7" t="n"/>
+      <c r="C135" s="8" t="n"/>
+      <c r="D135" s="8" t="n"/>
+      <c r="E135" s="22" t="str">
+        <f>IF(AND(A135&amp;""="",B135&amp;""="",N(C135)=0,N(D135)=0),"",IF(COUNTIF($G$8:$G$20,B135&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="7" t="n"/>
+      <c r="C136" s="8" t="n"/>
+      <c r="D136" s="8" t="n"/>
+      <c r="E136" s="22" t="str">
+        <f>IF(AND(A136&amp;""="",B136&amp;""="",N(C136)=0,N(D136)=0),"",IF(COUNTIF($G$8:$G$20,B136&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" s="7" t="n"/>
+      <c r="C137" s="8" t="n"/>
+      <c r="D137" s="8" t="n"/>
+      <c r="E137" s="22" t="str">
+        <f>IF(AND(A137&amp;""="",B137&amp;""="",N(C137)=0,N(D137)=0),"",IF(COUNTIF($G$8:$G$20,B137&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" s="7" t="n"/>
+      <c r="C138" s="8" t="n"/>
+      <c r="D138" s="8" t="n"/>
+      <c r="E138" s="22" t="str">
+        <f>IF(AND(A138&amp;""="",B138&amp;""="",N(C138)=0,N(D138)=0),"",IF(COUNTIF($G$8:$G$20,B138&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="7" t="n"/>
+      <c r="C139" s="8" t="n"/>
+      <c r="D139" s="8" t="n"/>
+      <c r="E139" s="22" t="str">
+        <f>IF(AND(A139&amp;""="",B139&amp;""="",N(C139)=0,N(D139)=0),"",IF(COUNTIF($G$8:$G$20,B139&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" s="7" t="n"/>
+      <c r="C140" s="8" t="n"/>
+      <c r="D140" s="8" t="n"/>
+      <c r="E140" s="22" t="str">
+        <f>IF(AND(A140&amp;""="",B140&amp;""="",N(C140)=0,N(D140)=0),"",IF(COUNTIF($G$8:$G$20,B140&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" s="7" t="n"/>
+      <c r="C141" s="8" t="n"/>
+      <c r="D141" s="8" t="n"/>
+      <c r="E141" s="22" t="str">
+        <f>IF(AND(A141&amp;""="",B141&amp;""="",N(C141)=0,N(D141)=0),"",IF(COUNTIF($G$8:$G$20,B141&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" s="7" t="n"/>
+      <c r="C142" s="8" t="n"/>
+      <c r="D142" s="8" t="n"/>
+      <c r="E142" s="22" t="str">
+        <f>IF(AND(A142&amp;""="",B142&amp;""="",N(C142)=0,N(D142)=0),"",IF(COUNTIF($G$8:$G$20,B142&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" s="7" t="n"/>
+      <c r="C143" s="8" t="n"/>
+      <c r="D143" s="8" t="n"/>
+      <c r="E143" s="22" t="str">
+        <f>IF(AND(A143&amp;""="",B143&amp;""="",N(C143)=0,N(D143)=0),"",IF(COUNTIF($G$8:$G$20,B143&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" s="7" t="n"/>
+      <c r="C144" s="8" t="n"/>
+      <c r="D144" s="8" t="n"/>
+      <c r="E144" s="22" t="str">
+        <f>IF(AND(A144&amp;""="",B144&amp;""="",N(C144)=0,N(D144)=0),"",IF(COUNTIF($G$8:$G$20,B144&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" s="7" t="n"/>
+      <c r="C145" s="8" t="n"/>
+      <c r="D145" s="8" t="n"/>
+      <c r="E145" s="22" t="str">
+        <f>IF(AND(A145&amp;""="",B145&amp;""="",N(C145)=0,N(D145)=0),"",IF(COUNTIF($G$8:$G$20,B145&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" s="7" t="n"/>
+      <c r="C146" s="8" t="n"/>
+      <c r="D146" s="8" t="n"/>
+      <c r="E146" s="22" t="str">
+        <f>IF(AND(A146&amp;""="",B146&amp;""="",N(C146)=0,N(D146)=0),"",IF(COUNTIF($G$8:$G$20,B146&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" s="7" t="n"/>
+      <c r="C147" s="8" t="n"/>
+      <c r="D147" s="8" t="n"/>
+      <c r="E147" s="22" t="str">
+        <f>IF(AND(A147&amp;""="",B147&amp;""="",N(C147)=0,N(D147)=0),"",IF(COUNTIF($G$8:$G$20,B147&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" s="7" t="n"/>
+      <c r="C148" s="8" t="n"/>
+      <c r="D148" s="8" t="n"/>
+      <c r="E148" s="22" t="str">
+        <f>IF(AND(A148&amp;""="",B148&amp;""="",N(C148)=0,N(D148)=0),"",IF(COUNTIF($G$8:$G$20,B148&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" s="7" t="n"/>
+      <c r="C149" s="8" t="n"/>
+      <c r="D149" s="8" t="n"/>
+      <c r="E149" s="22" t="str">
+        <f>IF(AND(A149&amp;""="",B149&amp;""="",N(C149)=0,N(D149)=0),"",IF(COUNTIF($G$8:$G$20,B149&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" s="7" t="n"/>
+      <c r="C150" s="8" t="n"/>
+      <c r="D150" s="8" t="n"/>
+      <c r="E150" s="22" t="str">
+        <f>IF(AND(A150&amp;""="",B150&amp;""="",N(C150)=0,N(D150)=0),"",IF(COUNTIF($G$8:$G$20,B150&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" s="7" t="n"/>
+      <c r="C151" s="8" t="n"/>
+      <c r="D151" s="8" t="n"/>
+      <c r="E151" s="22" t="str">
+        <f>IF(AND(A151&amp;""="",B151&amp;""="",N(C151)=0,N(D151)=0),"",IF(COUNTIF($G$8:$G$20,B151&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" s="7" t="n"/>
+      <c r="C152" s="8" t="n"/>
+      <c r="D152" s="8" t="n"/>
+      <c r="E152" s="22" t="str">
+        <f>IF(AND(A152&amp;""="",B152&amp;""="",N(C152)=0,N(D152)=0),"",IF(COUNTIF($G$8:$G$20,B152&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" s="7" t="n"/>
+      <c r="C153" s="8" t="n"/>
+      <c r="D153" s="8" t="n"/>
+      <c r="E153" s="22" t="str">
+        <f>IF(AND(A153&amp;""="",B153&amp;""="",N(C153)=0,N(D153)=0),"",IF(COUNTIF($G$8:$G$20,B153&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" s="7" t="n"/>
+      <c r="C154" s="8" t="n"/>
+      <c r="D154" s="8" t="n"/>
+      <c r="E154" s="22" t="str">
+        <f>IF(AND(A154&amp;""="",B154&amp;""="",N(C154)=0,N(D154)=0),"",IF(COUNTIF($G$8:$G$20,B154&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" s="7" t="n"/>
+      <c r="C155" s="8" t="n"/>
+      <c r="D155" s="8" t="n"/>
+      <c r="E155" s="22" t="str">
+        <f>IF(AND(A155&amp;""="",B155&amp;""="",N(C155)=0,N(D155)=0),"",IF(COUNTIF($G$8:$G$20,B155&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" s="7" t="n"/>
+      <c r="C156" s="8" t="n"/>
+      <c r="D156" s="8" t="n"/>
+      <c r="E156" s="22" t="str">
+        <f>IF(AND(A156&amp;""="",B156&amp;""="",N(C156)=0,N(D156)=0),"",IF(COUNTIF($G$8:$G$20,B156&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" s="7" t="n"/>
+      <c r="C157" s="8" t="n"/>
+      <c r="D157" s="8" t="n"/>
+      <c r="E157" s="22" t="str">
+        <f>IF(AND(A157&amp;""="",B157&amp;""="",N(C157)=0,N(D157)=0),"",IF(COUNTIF($G$8:$G$20,B157&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" s="7" t="n"/>
+      <c r="C158" s="8" t="n"/>
+      <c r="D158" s="8" t="n"/>
+      <c r="E158" s="22" t="str">
+        <f>IF(AND(A158&amp;""="",B158&amp;""="",N(C158)=0,N(D158)=0),"",IF(COUNTIF($G$8:$G$20,B158&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" s="7" t="n"/>
+      <c r="C159" s="8" t="n"/>
+      <c r="D159" s="8" t="n"/>
+      <c r="E159" s="22" t="str">
+        <f>IF(AND(A159&amp;""="",B159&amp;""="",N(C159)=0,N(D159)=0),"",IF(COUNTIF($G$8:$G$20,B159&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" s="7" t="n"/>
+      <c r="C160" s="8" t="n"/>
+      <c r="D160" s="8" t="n"/>
+      <c r="E160" s="22" t="str">
+        <f>IF(AND(A160&amp;""="",B160&amp;""="",N(C160)=0,N(D160)=0),"",IF(COUNTIF($G$8:$G$20,B160&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" s="7" t="n"/>
+      <c r="C161" s="8" t="n"/>
+      <c r="D161" s="8" t="n"/>
+      <c r="E161" s="22" t="str">
+        <f>IF(AND(A161&amp;""="",B161&amp;""="",N(C161)=0,N(D161)=0),"",IF(COUNTIF($G$8:$G$20,B161&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" s="7" t="n"/>
+      <c r="C162" s="8" t="n"/>
+      <c r="D162" s="8" t="n"/>
+      <c r="E162" s="22" t="str">
+        <f>IF(AND(A162&amp;""="",B162&amp;""="",N(C162)=0,N(D162)=0),"",IF(COUNTIF($G$8:$G$20,B162&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" s="7" t="n"/>
+      <c r="C163" s="8" t="n"/>
+      <c r="D163" s="8" t="n"/>
+      <c r="E163" s="22" t="str">
+        <f>IF(AND(A163&amp;""="",B163&amp;""="",N(C163)=0,N(D163)=0),"",IF(COUNTIF($G$8:$G$20,B163&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" s="7" t="n"/>
+      <c r="C164" s="8" t="n"/>
+      <c r="D164" s="8" t="n"/>
+      <c r="E164" s="22" t="str">
+        <f>IF(AND(A164&amp;""="",B164&amp;""="",N(C164)=0,N(D164)=0),"",IF(COUNTIF($G$8:$G$20,B164&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" s="7" t="n"/>
+      <c r="C165" s="8" t="n"/>
+      <c r="D165" s="8" t="n"/>
+      <c r="E165" s="22" t="str">
+        <f>IF(AND(A165&amp;""="",B165&amp;""="",N(C165)=0,N(D165)=0),"",IF(COUNTIF($G$8:$G$20,B165&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" s="7" t="n"/>
+      <c r="C166" s="8" t="n"/>
+      <c r="D166" s="8" t="n"/>
+      <c r="E166" s="22" t="str">
+        <f>IF(AND(A166&amp;""="",B166&amp;""="",N(C166)=0,N(D166)=0),"",IF(COUNTIF($G$8:$G$20,B166&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" s="7" t="n"/>
+      <c r="C167" s="8" t="n"/>
+      <c r="D167" s="8" t="n"/>
+      <c r="E167" s="22" t="str">
+        <f>IF(AND(A167&amp;""="",B167&amp;""="",N(C167)=0,N(D167)=0),"",IF(COUNTIF($G$8:$G$20,B167&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" s="7" t="n"/>
+      <c r="C168" s="8" t="n"/>
+      <c r="D168" s="8" t="n"/>
+      <c r="E168" s="22" t="str">
+        <f>IF(AND(A168&amp;""="",B168&amp;""="",N(C168)=0,N(D168)=0),"",IF(COUNTIF($G$8:$G$20,B168&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" s="7" t="n"/>
+      <c r="C169" s="8" t="n"/>
+      <c r="D169" s="8" t="n"/>
+      <c r="E169" s="22" t="str">
+        <f>IF(AND(A169&amp;""="",B169&amp;""="",N(C169)=0,N(D169)=0),"",IF(COUNTIF($G$8:$G$20,B169&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" s="7" t="n"/>
+      <c r="C170" s="8" t="n"/>
+      <c r="D170" s="8" t="n"/>
+      <c r="E170" s="22" t="str">
+        <f>IF(AND(A170&amp;""="",B170&amp;""="",N(C170)=0,N(D170)=0),"",IF(COUNTIF($G$8:$G$20,B170&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" s="7" t="n"/>
+      <c r="C171" s="8" t="n"/>
+      <c r="D171" s="8" t="n"/>
+      <c r="E171" s="22" t="str">
+        <f>IF(AND(A171&amp;""="",B171&amp;""="",N(C171)=0,N(D171)=0),"",IF(COUNTIF($G$8:$G$20,B171&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" s="7" t="n"/>
+      <c r="C172" s="8" t="n"/>
+      <c r="D172" s="8" t="n"/>
+      <c r="E172" s="22" t="str">
+        <f>IF(AND(A172&amp;""="",B172&amp;""="",N(C172)=0,N(D172)=0),"",IF(COUNTIF($G$8:$G$20,B172&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" s="7" t="n"/>
+      <c r="C173" s="8" t="n"/>
+      <c r="D173" s="8" t="n"/>
+      <c r="E173" s="22" t="str">
+        <f>IF(AND(A173&amp;""="",B173&amp;""="",N(C173)=0,N(D173)=0),"",IF(COUNTIF($G$8:$G$20,B173&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" s="7" t="n"/>
+      <c r="C174" s="8" t="n"/>
+      <c r="D174" s="8" t="n"/>
+      <c r="E174" s="22" t="str">
+        <f>IF(AND(A174&amp;""="",B174&amp;""="",N(C174)=0,N(D174)=0),"",IF(COUNTIF($G$8:$G$20,B174&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" s="7" t="n"/>
+      <c r="C175" s="8" t="n"/>
+      <c r="D175" s="8" t="n"/>
+      <c r="E175" s="22" t="str">
+        <f>IF(AND(A175&amp;""="",B175&amp;""="",N(C175)=0,N(D175)=0),"",IF(COUNTIF($G$8:$G$20,B175&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" s="7" t="n"/>
+      <c r="C176" s="8" t="n"/>
+      <c r="D176" s="8" t="n"/>
+      <c r="E176" s="22" t="str">
+        <f>IF(AND(A176&amp;""="",B176&amp;""="",N(C176)=0,N(D176)=0),"",IF(COUNTIF($G$8:$G$20,B176&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" s="7" t="n"/>
+      <c r="C177" s="8" t="n"/>
+      <c r="D177" s="8" t="n"/>
+      <c r="E177" s="22" t="str">
+        <f>IF(AND(A177&amp;""="",B177&amp;""="",N(C177)=0,N(D177)=0),"",IF(COUNTIF($G$8:$G$20,B177&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" s="7" t="n"/>
+      <c r="C178" s="8" t="n"/>
+      <c r="D178" s="8" t="n"/>
+      <c r="E178" s="22" t="str">
+        <f>IF(AND(A178&amp;""="",B178&amp;""="",N(C178)=0,N(D178)=0),"",IF(COUNTIF($G$8:$G$20,B178&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" s="7" t="n"/>
+      <c r="C179" s="8" t="n"/>
+      <c r="D179" s="8" t="n"/>
+      <c r="E179" s="22" t="str">
+        <f>IF(AND(A179&amp;""="",B179&amp;""="",N(C179)=0,N(D179)=0),"",IF(COUNTIF($G$8:$G$20,B179&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" s="7" t="n"/>
+      <c r="C180" s="8" t="n"/>
+      <c r="D180" s="8" t="n"/>
+      <c r="E180" s="22" t="str">
+        <f>IF(AND(A180&amp;""="",B180&amp;""="",N(C180)=0,N(D180)=0),"",IF(COUNTIF($G$8:$G$20,B180&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" s="7" t="n"/>
+      <c r="C181" s="8" t="n"/>
+      <c r="D181" s="8" t="n"/>
+      <c r="E181" s="22" t="str">
+        <f>IF(AND(A181&amp;""="",B181&amp;""="",N(C181)=0,N(D181)=0),"",IF(COUNTIF($G$8:$G$20,B181&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" s="7" t="n"/>
+      <c r="C182" s="8" t="n"/>
+      <c r="D182" s="8" t="n"/>
+      <c r="E182" s="22" t="str">
+        <f>IF(AND(A182&amp;""="",B182&amp;""="",N(C182)=0,N(D182)=0),"",IF(COUNTIF($G$8:$G$20,B182&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" s="7" t="n"/>
+      <c r="C183" s="8" t="n"/>
+      <c r="D183" s="8" t="n"/>
+      <c r="E183" s="22" t="str">
+        <f>IF(AND(A183&amp;""="",B183&amp;""="",N(C183)=0,N(D183)=0),"",IF(COUNTIF($G$8:$G$20,B183&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" s="7" t="n"/>
+      <c r="C184" s="8" t="n"/>
+      <c r="D184" s="8" t="n"/>
+      <c r="E184" s="22" t="str">
+        <f>IF(AND(A184&amp;""="",B184&amp;""="",N(C184)=0,N(D184)=0),"",IF(COUNTIF($G$8:$G$20,B184&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" s="7" t="n"/>
+      <c r="C185" s="8" t="n"/>
+      <c r="D185" s="8" t="n"/>
+      <c r="E185" s="22" t="str">
+        <f>IF(AND(A185&amp;""="",B185&amp;""="",N(C185)=0,N(D185)=0),"",IF(COUNTIF($G$8:$G$20,B185&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" s="7" t="n"/>
+      <c r="C186" s="8" t="n"/>
+      <c r="D186" s="8" t="n"/>
+      <c r="E186" s="22" t="str">
+        <f>IF(AND(A186&amp;""="",B186&amp;""="",N(C186)=0,N(D186)=0),"",IF(COUNTIF($G$8:$G$20,B186&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" s="7" t="n"/>
+      <c r="C187" s="8" t="n"/>
+      <c r="D187" s="8" t="n"/>
+      <c r="E187" s="22" t="str">
+        <f>IF(AND(A187&amp;""="",B187&amp;""="",N(C187)=0,N(D187)=0),"",IF(COUNTIF($G$8:$G$20,B187&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" s="7" t="n"/>
+      <c r="C188" s="8" t="n"/>
+      <c r="D188" s="8" t="n"/>
+      <c r="E188" s="22" t="str">
+        <f>IF(AND(A188&amp;""="",B188&amp;""="",N(C188)=0,N(D188)=0),"",IF(COUNTIF($G$8:$G$20,B188&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" s="7" t="n"/>
+      <c r="C189" s="8" t="n"/>
+      <c r="D189" s="8" t="n"/>
+      <c r="E189" s="22" t="str">
+        <f>IF(AND(A189&amp;""="",B189&amp;""="",N(C189)=0,N(D189)=0),"",IF(COUNTIF($G$8:$G$20,B189&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" s="7" t="n"/>
+      <c r="C190" s="8" t="n"/>
+      <c r="D190" s="8" t="n"/>
+      <c r="E190" s="22" t="str">
+        <f>IF(AND(A190&amp;""="",B190&amp;""="",N(C190)=0,N(D190)=0),"",IF(COUNTIF($G$8:$G$20,B190&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" s="7" t="n"/>
+      <c r="C191" s="8" t="n"/>
+      <c r="D191" s="8" t="n"/>
+      <c r="E191" s="22" t="str">
+        <f>IF(AND(A191&amp;""="",B191&amp;""="",N(C191)=0,N(D191)=0),"",IF(COUNTIF($G$8:$G$20,B191&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" s="7" t="n"/>
+      <c r="C192" s="8" t="n"/>
+      <c r="D192" s="8" t="n"/>
+      <c r="E192" s="22" t="str">
+        <f>IF(AND(A192&amp;""="",B192&amp;""="",N(C192)=0,N(D192)=0),"",IF(COUNTIF($G$8:$G$20,B192&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" s="7" t="n"/>
+      <c r="C193" s="8" t="n"/>
+      <c r="D193" s="8" t="n"/>
+      <c r="E193" s="22" t="str">
+        <f>IF(AND(A193&amp;""="",B193&amp;""="",N(C193)=0,N(D193)=0),"",IF(COUNTIF($G$8:$G$20,B193&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" s="7" t="n"/>
+      <c r="C194" s="8" t="n"/>
+      <c r="D194" s="8" t="n"/>
+      <c r="E194" s="22" t="str">
+        <f>IF(AND(A194&amp;""="",B194&amp;""="",N(C194)=0,N(D194)=0),"",IF(COUNTIF($G$8:$G$20,B194&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" s="7" t="n"/>
+      <c r="C195" s="8" t="n"/>
+      <c r="D195" s="8" t="n"/>
+      <c r="E195" s="22" t="str">
+        <f>IF(AND(A195&amp;""="",B195&amp;""="",N(C195)=0,N(D195)=0),"",IF(COUNTIF($G$8:$G$20,B195&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" s="7" t="n"/>
+      <c r="C196" s="8" t="n"/>
+      <c r="D196" s="8" t="n"/>
+      <c r="E196" s="22" t="str">
+        <f>IF(AND(A196&amp;""="",B196&amp;""="",N(C196)=0,N(D196)=0),"",IF(COUNTIF($G$8:$G$20,B196&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" s="7" t="n"/>
+      <c r="C197" s="8" t="n"/>
+      <c r="D197" s="8" t="n"/>
+      <c r="E197" s="22" t="str">
+        <f>IF(AND(A197&amp;""="",B197&amp;""="",N(C197)=0,N(D197)=0),"",IF(COUNTIF($G$8:$G$20,B197&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" s="7" t="n"/>
+      <c r="C198" s="8" t="n"/>
+      <c r="D198" s="8" t="n"/>
+      <c r="E198" s="22" t="str">
+        <f>IF(AND(A198&amp;""="",B198&amp;""="",N(C198)=0,N(D198)=0),"",IF(COUNTIF($G$8:$G$20,B198&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" s="7" t="n"/>
+      <c r="C199" s="8" t="n"/>
+      <c r="D199" s="8" t="n"/>
+      <c r="E199" s="22" t="str">
+        <f>IF(AND(A199&amp;""="",B199&amp;""="",N(C199)=0,N(D199)=0),"",IF(COUNTIF($G$8:$G$20,B199&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" s="7" t="n"/>
+      <c r="C200" s="8" t="n"/>
+      <c r="D200" s="8" t="n"/>
+      <c r="E200" s="22" t="str">
+        <f>IF(AND(A200&amp;""="",B200&amp;""="",N(C200)=0,N(D200)=0),"",IF(COUNTIF($G$8:$G$20,B200&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" s="7" t="n"/>
+      <c r="C201" s="8" t="n"/>
+      <c r="D201" s="8" t="n"/>
+      <c r="E201" s="22" t="str">
+        <f>IF(AND(A201&amp;""="",B201&amp;""="",N(C201)=0,N(D201)=0),"",IF(COUNTIF($G$8:$G$20,B201&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" s="7" t="n"/>
+      <c r="C202" s="8" t="n"/>
+      <c r="D202" s="8" t="n"/>
+      <c r="E202" s="22" t="str">
+        <f>IF(AND(A202&amp;""="",B202&amp;""="",N(C202)=0,N(D202)=0),"",IF(COUNTIF($G$8:$G$20,B202&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" s="7" t="n"/>
+      <c r="C203" s="8" t="n"/>
+      <c r="D203" s="8" t="n"/>
+      <c r="E203" s="22" t="str">
+        <f>IF(AND(A203&amp;""="",B203&amp;""="",N(C203)=0,N(D203)=0),"",IF(COUNTIF($G$8:$G$20,B203&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" s="7" t="n"/>
+      <c r="C204" s="8" t="n"/>
+      <c r="D204" s="8" t="n"/>
+      <c r="E204" s="22" t="str">
+        <f>IF(AND(A204&amp;""="",B204&amp;""="",N(C204)=0,N(D204)=0),"",IF(COUNTIF($G$8:$G$20,B204&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" s="7" t="n"/>
+      <c r="C205" s="8" t="n"/>
+      <c r="D205" s="8" t="n"/>
+      <c r="E205" s="22" t="str">
+        <f>IF(AND(A205&amp;""="",B205&amp;""="",N(C205)=0,N(D205)=0),"",IF(COUNTIF($G$8:$G$20,B205&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" s="7" t="n"/>
+      <c r="C206" s="8" t="n"/>
+      <c r="D206" s="8" t="n"/>
+      <c r="E206" s="22" t="str">
+        <f>IF(AND(A206&amp;""="",B206&amp;""="",N(C206)=0,N(D206)=0),"",IF(COUNTIF($G$8:$G$20,B206&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" s="7" t="n"/>
+      <c r="C207" s="8" t="n"/>
+      <c r="D207" s="8" t="n"/>
+      <c r="E207" s="22" t="str">
+        <f>IF(AND(A207&amp;""="",B207&amp;""="",N(C207)=0,N(D207)=0),"",IF(COUNTIF($G$8:$G$20,B207&amp;"")&gt;0,"OK","CHECK CATEGORY"))</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1195,9 +2953,15 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A5:B5"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="B8:B37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid category" error="Pick a category from the list." type="list">
-      <formula1>"Revenue,COGS,Operating Expenses,Depreciation &amp; Amortisation,Interest Expense,Tax Expense,Cash,Other Current Assets,Non-Current Assets,Current Liabilities,Non-Current Liabilities,Share Capital,Drawings/Dividends Paid"</formula1>
+  <dataValidations count="3">
+    <dataValidation sqref="B8:B207" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Category not recognised" error="Pick a category from the list so the statements pick this account up." type="list">
+      <formula1>=$G$8:$G$20</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Sole trader,Partnership,Company,Trust"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Cash,Accruals,Not registered"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1211,7 +2975,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -1233,6 +2997,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="9" t="inlineStr"/>
       <c r="B4" s="9" t="inlineStr">
@@ -1258,12 +3023,12 @@
         </is>
       </c>
       <c r="B5" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Revenue",'Trial Balance Input'!$C$8:$C$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Revenue",'Trial Balance Input'!$C$8:$C$207)</f>
+        <v>380000</v>
       </c>
       <c r="C5" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Revenue",'Trial Balance Input'!$D$8:$D$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Revenue",'Trial Balance Input'!$D$8:$D$207)</f>
+        <v>450000</v>
       </c>
     </row>
     <row r="6">
@@ -1273,12 +3038,12 @@
         </is>
       </c>
       <c r="B6" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"COGS",'Trial Balance Input'!$C$8:$C$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"COGS",'Trial Balance Input'!$C$8:$C$207)</f>
+        <v>190000</v>
       </c>
       <c r="C6" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"COGS",'Trial Balance Input'!$D$8:$D$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"COGS",'Trial Balance Input'!$D$8:$D$207)</f>
+        <v>220000</v>
       </c>
     </row>
     <row r="7">
@@ -1289,17 +3054,18 @@
       </c>
       <c r="B7" s="14">
         <f>B5-B6</f>
-        <v/>
+        <v>190000</v>
       </c>
       <c r="C7" s="14">
         <f>C5-C6</f>
-        <v/>
+        <v>230000</v>
       </c>
       <c r="D7" s="15">
         <f>IFERROR((C7-B7)/ABS(B7),"-")</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.21052631578947367</v>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
@@ -1307,12 +3073,12 @@
         </is>
       </c>
       <c r="B9" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Operating Expenses",'Trial Balance Input'!$C$8:$C$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Operating Expenses",'Trial Balance Input'!$C$8:$C$207)</f>
+        <v>142000</v>
       </c>
       <c r="C9" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Operating Expenses",'Trial Balance Input'!$D$8:$D$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Operating Expenses",'Trial Balance Input'!$D$8:$D$207)</f>
+        <v>163000</v>
       </c>
     </row>
     <row r="10">
@@ -1322,12 +3088,12 @@
         </is>
       </c>
       <c r="B10" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Depreciation &amp; Amortisation",'Trial Balance Input'!$C$8:$C$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Depreciation &amp; Amortisation",'Trial Balance Input'!$C$8:$C$207)</f>
+        <v>12000</v>
       </c>
       <c r="C10" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Depreciation &amp; Amortisation",'Trial Balance Input'!$D$8:$D$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Depreciation &amp; Amortisation",'Trial Balance Input'!$D$8:$D$207)</f>
+        <v>14000</v>
       </c>
     </row>
     <row r="11">
@@ -1338,17 +3104,18 @@
       </c>
       <c r="B11" s="14">
         <f>B7-B9-B10</f>
-        <v/>
+        <v>36000</v>
       </c>
       <c r="C11" s="14">
         <f>C7-C9-C10</f>
-        <v/>
+        <v>53000</v>
       </c>
       <c r="D11" s="15">
         <f>IFERROR((C11-B11)/ABS(B11),"-")</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.4722222222222222</v>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -1356,12 +3123,12 @@
         </is>
       </c>
       <c r="B13" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Interest Expense",'Trial Balance Input'!$C$8:$C$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Interest Expense",'Trial Balance Input'!$C$8:$C$207)</f>
+        <v>5000</v>
       </c>
       <c r="C13" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Interest Expense",'Trial Balance Input'!$D$8:$D$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Interest Expense",'Trial Balance Input'!$D$8:$D$207)</f>
+        <v>4500</v>
       </c>
     </row>
     <row r="14">
@@ -1372,17 +3139,18 @@
       </c>
       <c r="B14" s="14">
         <f>B11-B13</f>
-        <v/>
+        <v>31000</v>
       </c>
       <c r="C14" s="14">
         <f>C11-C13</f>
-        <v/>
+        <v>48500</v>
       </c>
       <c r="D14" s="15">
         <f>IFERROR((C14-B14)/ABS(B14),"-")</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.5645161290322581</v>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
@@ -1390,12 +3158,12 @@
         </is>
       </c>
       <c r="B16" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Tax Expense",'Trial Balance Input'!$C$8:$C$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Tax Expense",'Trial Balance Input'!$C$8:$C$207)</f>
+        <v>8000</v>
       </c>
       <c r="C16" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Tax Expense",'Trial Balance Input'!$D$8:$D$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Tax Expense",'Trial Balance Input'!$D$8:$D$207)</f>
+        <v>12000</v>
       </c>
     </row>
     <row r="17">
@@ -1406,17 +3174,19 @@
       </c>
       <c r="B17" s="14">
         <f>B14-B16</f>
-        <v/>
+        <v>23000</v>
       </c>
       <c r="C17" s="14">
         <f>C14-C16</f>
-        <v/>
+        <v>36500</v>
       </c>
       <c r="D17" s="15">
         <f>IFERROR((C17-B17)/ABS(B17),"-")</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.5869565217391305</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
@@ -1425,11 +3195,11 @@
       </c>
       <c r="B20" s="16">
         <f>IFERROR(B7/B5,"-")</f>
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="C20" s="16">
         <f>IFERROR(C7/C5,"-")</f>
-        <v/>
+        <v>0.5111111111111111</v>
       </c>
     </row>
     <row r="21">
@@ -1440,11 +3210,11 @@
       </c>
       <c r="B21" s="16">
         <f>IFERROR(B17/B5,"-")</f>
-        <v/>
+        <v>0.060526315789473685</v>
       </c>
       <c r="C21" s="16">
         <f>IFERROR(C17/C5,"-")</f>
-        <v/>
+        <v>0.0811111111111111</v>
       </c>
     </row>
   </sheetData>
@@ -1462,8 +3232,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -1485,6 +3255,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="9" t="inlineStr"/>
       <c r="B4" s="9" t="inlineStr">
@@ -1513,12 +3284,12 @@
         </is>
       </c>
       <c r="B6" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Cash",'Trial Balance Input'!$C$8:$C$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Cash",'Trial Balance Input'!$C$8:$C$207)</f>
+        <v>48000</v>
       </c>
       <c r="C6" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Cash",'Trial Balance Input'!$D$8:$D$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Cash",'Trial Balance Input'!$D$8:$D$207)</f>
+        <v>39000</v>
       </c>
     </row>
     <row r="7">
@@ -1528,12 +3299,12 @@
         </is>
       </c>
       <c r="B7" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Other Current Assets",'Trial Balance Input'!$C$8:$C$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Other Current Assets",'Trial Balance Input'!$C$8:$C$207)</f>
+        <v>73000</v>
       </c>
       <c r="C7" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Other Current Assets",'Trial Balance Input'!$D$8:$D$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Other Current Assets",'Trial Balance Input'!$D$8:$D$207)</f>
+        <v>86000</v>
       </c>
     </row>
     <row r="8">
@@ -1544,11 +3315,11 @@
       </c>
       <c r="B8" s="14">
         <f>B6+B7</f>
-        <v/>
+        <v>121000</v>
       </c>
       <c r="C8" s="14">
         <f>C6+C7</f>
-        <v/>
+        <v>125000</v>
       </c>
     </row>
     <row r="9">
@@ -1558,12 +3329,12 @@
         </is>
       </c>
       <c r="B9" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Non-Current Assets",'Trial Balance Input'!$C$8:$C$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Non-Current Assets",'Trial Balance Input'!$C$8:$C$207)</f>
+        <v>60000</v>
       </c>
       <c r="C9" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Non-Current Assets",'Trial Balance Input'!$D$8:$D$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Non-Current Assets",'Trial Balance Input'!$D$8:$D$207)</f>
+        <v>70000</v>
       </c>
     </row>
     <row r="10">
@@ -1574,13 +3345,14 @@
       </c>
       <c r="B10" s="14">
         <f>B8+B9</f>
-        <v/>
+        <v>181000</v>
       </c>
       <c r="C10" s="14">
         <f>C8+C9</f>
-        <v/>
-      </c>
-    </row>
+        <v>195000</v>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -1595,12 +3367,12 @@
         </is>
       </c>
       <c r="B13" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Current Liabilities",'Trial Balance Input'!$C$8:$C$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Current Liabilities",'Trial Balance Input'!$C$8:$C$207)</f>
+        <v>28000</v>
       </c>
       <c r="C13" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Current Liabilities",'Trial Balance Input'!$D$8:$D$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Current Liabilities",'Trial Balance Input'!$D$8:$D$207)</f>
+        <v>33500</v>
       </c>
     </row>
     <row r="14">
@@ -1610,12 +3382,12 @@
         </is>
       </c>
       <c r="B14" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Non-Current Liabilities",'Trial Balance Input'!$C$8:$C$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Non-Current Liabilities",'Trial Balance Input'!$C$8:$C$207)</f>
+        <v>70000</v>
       </c>
       <c r="C14" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Non-Current Liabilities",'Trial Balance Input'!$D$8:$D$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Non-Current Liabilities",'Trial Balance Input'!$D$8:$D$207)</f>
+        <v>60000</v>
       </c>
     </row>
     <row r="15">
@@ -1626,13 +3398,14 @@
       </c>
       <c r="B15" s="14">
         <f>B13+B14</f>
-        <v/>
+        <v>98000</v>
       </c>
       <c r="C15" s="14">
         <f>C13+C14</f>
-        <v/>
-      </c>
-    </row>
+        <v>93500</v>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
@@ -1641,33 +3414,31 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Share Capital</t>
-        </is>
+      <c r="A18" s="11" t="str">
+        <f>IF('Trial Balance Input'!$B$6="Company","    Share Capital","    Owner's Capital")</f>
+        <v>    Share Capital</v>
       </c>
       <c r="B18" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Share Capital",'Trial Balance Input'!$C$8:$C$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Share Capital",'Trial Balance Input'!$C$8:$C$207)</f>
+        <v>50000</v>
       </c>
       <c r="C18" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Share Capital",'Trial Balance Input'!$D$8:$D$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Share Capital",'Trial Balance Input'!$D$8:$D$207)</f>
+        <v>50000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    (memo) Drawings/Dividends Paid in the period</t>
-        </is>
+      <c r="A19" s="11" t="str">
+        <f>IF('Trial Balance Input'!$B$6="Company","    (memo) Dividends paid in the period","    (memo) Owner drawings in the period")</f>
+        <v>    (memo) Dividends paid in the period</v>
       </c>
       <c r="B19" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Drawings/Dividends Paid",'Trial Balance Input'!$C$8:$C$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Drawings/Dividends Paid",'Trial Balance Input'!$C$8:$C$207)</f>
+        <v>15000</v>
       </c>
       <c r="C19" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Drawings/Dividends Paid",'Trial Balance Input'!$D$8:$D$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Drawings/Dividends Paid",'Trial Balance Input'!$D$8:$D$207)</f>
+        <v>18000</v>
       </c>
     </row>
     <row r="20">
@@ -1678,11 +3449,11 @@
       </c>
       <c r="B20" s="12">
         <f>'Trial Balance Input'!$C$5+'P&amp;L'!B17-B19</f>
-        <v/>
+        <v>33000</v>
       </c>
       <c r="C20" s="12">
         <f>B20+'P&amp;L'!C17-C19</f>
-        <v/>
+        <v>51500</v>
       </c>
     </row>
     <row r="21">
@@ -1693,13 +3464,14 @@
       </c>
       <c r="B21" s="14">
         <f>B18+B20</f>
-        <v/>
+        <v>83000</v>
       </c>
       <c r="C21" s="14">
         <f>C18+C20</f>
-        <v/>
-      </c>
-    </row>
+        <v>101500</v>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
@@ -1708,13 +3480,14 @@
       </c>
       <c r="B23" s="14">
         <f>B15+B21</f>
-        <v/>
+        <v>181000</v>
       </c>
       <c r="C23" s="14">
         <f>C15+C21</f>
-        <v/>
-      </c>
-    </row>
+        <v>195000</v>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
@@ -1723,17 +3496,29 @@
       </c>
       <c r="B25" s="12">
         <f>B10-B23</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C25" s="12">
         <f>C10-C23</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17">
+      <c r="A26" s="17" t="str">
         <f>IF(AND(ABS(B25)&lt;1,ABS(C25)&lt;1),"TIES — Assets = Liabilities + Equity, both periods","EXCEPTION — does not balance, review the trial balance categorisation")</f>
-        <v/>
+        <v>TIES — Assets = Liabilities + Equity, both periods</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="str">
+        <f>IF('Trial Balance Input'!$B$3=0,"All trial balance rows categorised","EXCEPTION — "&amp;'Trial Balance Input'!$B$3&amp;" trial balance row(s) have a missing or misspelled category (Input tab, column E)")</f>
+        <v>All trial balance rows categorised</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="str">
+        <f>IF('Trial Balance Input'!$B$6="Company","Company: confirm the Dividends line holds declared dividends only. Money the owner takes out otherwise is a director loan — review Division 7A.","")</f>
+        <v>Company: confirm the Dividends line holds declared dividends only. Money the owner takes out otherwise is a director loan — review Division 7A.</v>
       </c>
     </row>
   </sheetData>
@@ -1753,7 +3538,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -1774,6 +3559,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="9" t="inlineStr"/>
       <c r="B4" s="9" t="inlineStr">
@@ -1802,7 +3588,7 @@
       </c>
       <c r="B6" s="12">
         <f>'P&amp;L'!C17</f>
-        <v/>
+        <v>36500</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -1817,8 +3603,8 @@
         </is>
       </c>
       <c r="B7" s="12">
-        <f>SUMIF('Trial Balance Input'!$B$8:$B$27,"Depreciation &amp; Amortisation",'Trial Balance Input'!$D$8:$D$27)</f>
-        <v/>
+        <f>SUMIF('Trial Balance Input'!$B$8:$B$207,"Depreciation &amp; Amortisation",'Trial Balance Input'!$D$8:$D$207)</f>
+        <v>14000</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -1834,7 +3620,7 @@
       </c>
       <c r="B8" s="12">
         <f>-('Balance Sheet'!C7-'Balance Sheet'!B7)</f>
-        <v/>
+        <v>-13000</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -1850,7 +3636,7 @@
       </c>
       <c r="B9" s="12">
         <f>'Balance Sheet'!C13-'Balance Sheet'!B13</f>
-        <v/>
+        <v>5500</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -1866,10 +3652,11 @@
       </c>
       <c r="B10" s="14">
         <f>SUM(B6:B9)</f>
-        <v/>
+        <v>43000</v>
       </c>
       <c r="C10" s="2" t="inlineStr"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -1885,7 +3672,7 @@
       </c>
       <c r="B13" s="12">
         <f>-(('Balance Sheet'!C9-'Balance Sheet'!B9)+B7)</f>
-        <v/>
+        <v>-24000</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -1901,10 +3688,11 @@
       </c>
       <c r="B14" s="14">
         <f>B13</f>
-        <v/>
+        <v>-24000</v>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
@@ -1920,7 +3708,7 @@
       </c>
       <c r="B17" s="12">
         <f>'Balance Sheet'!C18-'Balance Sheet'!B18</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -1936,7 +3724,7 @@
       </c>
       <c r="B18" s="12">
         <f>-'Balance Sheet'!C19</f>
-        <v/>
+        <v>-18000</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -1952,7 +3740,7 @@
       </c>
       <c r="B19" s="12">
         <f>'Balance Sheet'!C14-'Balance Sheet'!B14</f>
-        <v/>
+        <v>-10000</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
@@ -1968,10 +3756,11 @@
       </c>
       <c r="B20" s="14">
         <f>SUM(B17:B19)</f>
-        <v/>
+        <v>-28000</v>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
@@ -1980,7 +3769,7 @@
       </c>
       <c r="B22" s="14">
         <f>B10+B14+B20</f>
-        <v/>
+        <v>-9000</v>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
     </row>
@@ -1992,7 +3781,7 @@
       </c>
       <c r="B23" s="12">
         <f>'Balance Sheet'!B6</f>
-        <v/>
+        <v>48000</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -2008,7 +3797,7 @@
       </c>
       <c r="B24" s="14">
         <f>B23+B22</f>
-        <v/>
+        <v>39000</v>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
     </row>
@@ -2020,7 +3809,7 @@
       </c>
       <c r="B25" s="12">
         <f>'Balance Sheet'!C6</f>
-        <v/>
+        <v>39000</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
@@ -2028,6 +3817,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -2036,13 +3826,13 @@
       </c>
       <c r="B27" s="12">
         <f>B24-B25</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17">
+      <c r="A28" s="17" t="str">
         <f>IF(ABS(B27)&lt;1,"TIES — computed closing cash equals the Balance Sheet cash balance","EXCEPTION — does not tie, review the trial balance categorisation")</f>
-        <v/>
+        <v>TIES — computed closing cash equals the Balance Sheet cash balance</v>
       </c>
     </row>
   </sheetData>
@@ -2084,6 +3874,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
@@ -2114,11 +3905,11 @@
       </c>
       <c r="B5" s="12">
         <f>'P&amp;L'!B5</f>
-        <v/>
+        <v>380000</v>
       </c>
       <c r="C5" s="12">
         <f>'P&amp;L'!C5</f>
-        <v/>
+        <v>450000</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -2134,11 +3925,11 @@
       </c>
       <c r="B6" s="12">
         <f>'P&amp;L'!B17</f>
-        <v/>
+        <v>23000</v>
       </c>
       <c r="C6" s="12">
         <f>'P&amp;L'!C17</f>
-        <v/>
+        <v>36500</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -2159,7 +3950,7 @@
       </c>
       <c r="C7" s="16">
         <f>IFERROR((C5-B5)/ABS(B5),"-")</f>
-        <v/>
+        <v>0.18421052631578946</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -2175,11 +3966,11 @@
       </c>
       <c r="B8" s="16">
         <f>'P&amp;L'!B20</f>
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="C8" s="16">
         <f>'P&amp;L'!C20</f>
-        <v/>
+        <v>0.5111111111111111</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -2195,11 +3986,11 @@
       </c>
       <c r="B9" s="16">
         <f>'P&amp;L'!B21</f>
-        <v/>
+        <v>0.060526315789473685</v>
       </c>
       <c r="C9" s="16">
         <f>'P&amp;L'!C21</f>
-        <v/>
+        <v>0.0811111111111111</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -2214,12 +4005,12 @@
         </is>
       </c>
       <c r="B10" s="19">
-        <f>'Balance Sheet'!B8/'Balance Sheet'!B13</f>
-        <v/>
+        <f>IFERROR('Balance Sheet'!B8/'Balance Sheet'!B13,"-")</f>
+        <v>4.321428571428571</v>
       </c>
       <c r="C10" s="19">
-        <f>'Balance Sheet'!C8/'Balance Sheet'!C13</f>
-        <v/>
+        <f>IFERROR('Balance Sheet'!C8/'Balance Sheet'!C13,"-")</f>
+        <v>3.7313432835820897</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -2234,12 +4025,12 @@
         </is>
       </c>
       <c r="B11" s="19">
-        <f>'Balance Sheet'!B6/'Balance Sheet'!B13</f>
-        <v/>
+        <f>IFERROR('Balance Sheet'!B6/'Balance Sheet'!B13,"-")</f>
+        <v>1.7142857142857142</v>
       </c>
       <c r="C11" s="19">
-        <f>'Balance Sheet'!C6/'Balance Sheet'!C13</f>
-        <v/>
+        <f>IFERROR('Balance Sheet'!C6/'Balance Sheet'!C13,"-")</f>
+        <v>1.164179104477612</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -2254,12 +4045,12 @@
         </is>
       </c>
       <c r="B12" s="19">
-        <f>'Balance Sheet'!B15/'Balance Sheet'!B21</f>
-        <v/>
+        <f>IFERROR('Balance Sheet'!B15/'Balance Sheet'!B21,"-")</f>
+        <v>1.180722891566265</v>
       </c>
       <c r="C12" s="19">
-        <f>'Balance Sheet'!C15/'Balance Sheet'!C21</f>
-        <v/>
+        <f>IFERROR('Balance Sheet'!C15/'Balance Sheet'!C21,"-")</f>
+        <v>0.9211822660098522</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -2276,7 +4067,7 @@
       <c r="B13" s="12" t="inlineStr"/>
       <c r="C13" s="12">
         <f>'Cash Flow'!B22</f>
-        <v/>
+        <v>-9000</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -2284,6 +4075,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="20" t="inlineStr">
         <is>
@@ -2299,4 +4091,173 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Monthly figures (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Blue cells only. Fill to draw the month-by-month charts on the client web dashboard. Totals must agree to the P&amp;L once all 12 months are in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Revenue ($)</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Net Profit ($)</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Cash at month end ($)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="n"/>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="n"/>
+      <c r="B6" s="24" t="n"/>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="24" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="n"/>
+      <c r="B7" s="24" t="n"/>
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="24" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="n"/>
+      <c r="B8" s="24" t="n"/>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="24" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="n"/>
+      <c r="B9" s="24" t="n"/>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="24" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="n"/>
+      <c r="B10" s="24" t="n"/>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="24" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="n"/>
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="n"/>
+      <c r="B12" s="24" t="n"/>
+      <c r="C12" s="24" t="n"/>
+      <c r="D12" s="24" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="n"/>
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="24" t="n"/>
+      <c r="D13" s="24" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="n"/>
+      <c r="B14" s="24" t="n"/>
+      <c r="C14" s="24" t="n"/>
+      <c r="D14" s="24" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="n"/>
+      <c r="B15" s="24" t="n"/>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="24" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="n"/>
+      <c r="B16" s="24" t="n"/>
+      <c r="C16" s="24" t="n"/>
+      <c r="D16" s="24" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B17" s="25">
+        <f>SUM(B5:B16)</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="25">
+        <f>SUM(C5:C16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Difference to P&amp;L (should be $0)</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="str">
+        <f>IF(COUNT(B5:B16)=12,B17-'P&amp;L'!C5,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="C19" s="26" t="str">
+        <f>IF(COUNT(C5:C16)=12,C17-'P&amp;L'!C17,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Last month cash vs Balance Sheet (should be $0)</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="str">
+        <f>IF(ISNUMBER(D16),D16-'Balance Sheet'!C6,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>